--- a/CoworkPlaybook/samples_tel/OneDrive_種入用/TEL2_企業專線/TEL2_企業專線月度中斷統計.xlsx
+++ b/CoworkPlaybook/samples_tel/OneDrive_種入用/TEL2_企業專線/TEL2_企業專線月度中斷統計.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +510,16 @@
           <t>備註</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>客戶窗口</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>窗口信箱</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -542,6 +554,16 @@
           <t>8/09 02:00-04:00 為事前公告之計畫性維護</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>資訊部 林經理</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -576,6 +598,16 @@
           <t>機房 UPS 異常</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>資訊部 陳副理</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -610,6 +642,16 @@
           <t>光纜遭施工挖斷</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>營運部 黃協理</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -644,6 +686,16 @@
           <t>短暫路由收斂</t>
         </is>
       </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MIS 吳主任</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -678,6 +730,16 @@
           <t>多次短時間閃斷累計</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>網路部 張經理</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -712,6 +774,16 @@
           <t>本月無中斷</t>
         </is>
       </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>資訊部 李課長</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -746,6 +818,16 @@
           <t>8/16 03:00-03:18 計畫性維護</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>總務部 周主任</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -778,6 +860,16 @@
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>用戶端設備電源故障</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>工務部 蔡工程師</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
         </is>
       </c>
     </row>
